--- a/evaluation/fairness_measure_based/OLS_Regression_Feature_Analysis_KS_Statistic_of_sensitive_attribute.xlsx
+++ b/evaluation/fairness_measure_based/OLS_Regression_Feature_Analysis_KS_Statistic_of_sensitive_attribute.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:J24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,28 +441,78 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>P-Value</t>
+          <t>t</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Significance</t>
+          <t>P-Value (raw)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>P-Value (Bonferroni)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Reject (Bonf@0.05)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Partial_R2</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Cohen_f2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Significance (raw)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Significance (bonf)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Dataset_ml1m</t>
+          <t>hit@5</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.142523018491469</v>
+        <v>0.03444029489632803</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0002810123639869121</v>
-      </c>
-      <c r="D2" t="inlineStr">
+        <v>4.512137735466622</v>
+      </c>
+      <c r="D2" t="n">
+        <v>7.288315429932837e-06</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.0001603429394585224</v>
+      </c>
+      <c r="F2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.02261251144715636</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.03625110909133977</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
         <is>
           <t>***</t>
         </is>
@@ -471,74 +521,146 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>const</t>
+          <t>Density</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1171983036949425</v>
+        <v>0.08210066301593774</v>
       </c>
       <c r="C3" t="n">
-        <v>1.183980216590531e-08</v>
-      </c>
-      <c r="D3" t="inlineStr">
+        <v>3.379061644183164</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.0007592969697213953</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.0167045333338707</v>
+      </c>
+      <c r="F3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.01280886952861683</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.02053446065483448</v>
+      </c>
+      <c r="I3" t="inlineStr">
         <is>
           <t>***</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>*</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>hit@5</t>
+          <t>Rating per Item</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.07191890217053779</v>
+        <v>-0.06617468937354888</v>
       </c>
       <c r="C4" t="n">
-        <v>5.648749680759733e-42</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>***</t>
+        <v>-3.190499479313115</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.001470578669124561</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.03235273072074035</v>
+      </c>
+      <c r="F4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.0114350974876439</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.01833210642981517</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>**</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>*</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sensitive Feature_Age</t>
+          <t>Rating per User</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.06348180075671321</v>
+        <v>-0.03484573218988005</v>
       </c>
       <c r="C5" t="n">
-        <v>9.630691893452015e-09</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>***</t>
-        </is>
-      </c>
+        <v>-3.053575882909397</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.002329366217948375</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.05124605679486425</v>
+      </c>
+      <c r="F5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.01048473026489293</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.01680853104327351</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>**</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sensitive Feature_Gender</t>
+          <t>Gini Item</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.05371650293822867</v>
+        <v>-0.0652475888957687</v>
       </c>
       <c r="C6" t="n">
-        <v>1.243791173888325e-07</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>***</t>
-        </is>
-      </c>
+        <v>-2.555863035765283</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.01075948738669268</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.2367087225072389</v>
+      </c>
+      <c r="F6" t="b">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.00736852436907415</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.01181280466655525</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -547,182 +669,356 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.04980259260715879</v>
+        <v>0.05154663389557718</v>
       </c>
       <c r="C7" t="n">
-        <v>0.06832677370102994</v>
-      </c>
-      <c r="D7" t="inlineStr"/>
+        <v>1.770379753321546</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.07701007195781036</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="b">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.003549001174615736</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.005689559474494688</v>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Shape</t>
+          <t>Dataset_BX</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.04358013532496434</v>
+        <v>-72043095917.80577</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01456126983058641</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>*</t>
-        </is>
-      </c>
+        <v>-1.637066282364882</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.1019741472482145</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="b">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.003036192114156469</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.004867452773203261</v>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Skewness of Long Tail Items</t>
+          <t>Model Name_PFCN_MLP</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.006332719966015069</v>
+        <v>-48308414865.71384</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5568743543234183</v>
-      </c>
-      <c r="D9" t="inlineStr"/>
+        <v>-1.637066282364583</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.1019741472482771</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="b">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.003036192114155362</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.004867452773201487</v>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Density</t>
+          <t>Sensitive Feature_Age</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.0003115319403869665</v>
+        <v>239193497139.0345</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9891719751403625</v>
-      </c>
-      <c r="D10" t="inlineStr"/>
+        <v>1.637066282364512</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.1019741472482919</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="b">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.003036192114155101</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.004867452773201067</v>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Skewness of Popularity Bias</t>
+          <t>Sensitive Feature_Gender</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.004661368561782082</v>
+        <v>239193497139.0316</v>
       </c>
       <c r="C11" t="n">
-        <v>0.6705242402660319</v>
-      </c>
-      <c r="D11" t="inlineStr"/>
+        <v>1.637066282364492</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.1019741472482961</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="b">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.003036192114155026</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.004867452773200947</v>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Number of Items</t>
+          <t>const</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.009269713847677424</v>
+        <v>-118841986355.4826</v>
       </c>
       <c r="C12" t="n">
-        <v>0.5589072660799643</v>
-      </c>
-      <c r="D12" t="inlineStr"/>
+        <v>-1.63706628236377</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.1019741472484469</v>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="b">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.003036192114152357</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.004867452773196669</v>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Standart Deviation of Rating</t>
+          <t>Model Name_NFCF</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.0229330413317579</v>
+        <v>-48308414865.68535</v>
       </c>
       <c r="C13" t="n">
-        <v>0.4774989454340225</v>
-      </c>
-      <c r="D13" t="inlineStr"/>
+        <v>-1.637066282363618</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.1019741472484786</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="b">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.003036192114151796</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.004867452773195769</v>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Dataset_BX</t>
+          <t>Model Name_FOCF</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.02532471479652698</v>
+        <v>-48308414865.68002</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3496247962868581</v>
-      </c>
-      <c r="D14" t="inlineStr"/>
+        <v>-1.637066282363429</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.1019741472485182</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="b">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.003036192114151096</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.004867452773194648</v>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Difference between Sensitive Attribute Percentage</t>
+          <t>Dataset_ml1m</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.02615873030948498</v>
+        <v>-72043095917.7195</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2694602978698377</v>
-      </c>
-      <c r="D15" t="inlineStr"/>
+        <v>-1.637066282362865</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.1019741472486359</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" t="b">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.003036192114149012</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.004867452773191306</v>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Gini User</t>
+          <t>Difference between Sensitive Attribute Percentage</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.03501135887587159</v>
+        <v>0.04059967824775728</v>
       </c>
       <c r="C16" t="n">
-        <v>0.02768153863024755</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>*</t>
-        </is>
-      </c>
+        <v>1.606422262705252</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.1085399030224022</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" t="b">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.002923917099565793</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.004687459771909714</v>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Rating per User</t>
+          <t>Mean Rating</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.04726367620400133</v>
+        <v>-0.0935160124297808</v>
       </c>
       <c r="C17" t="n">
-        <v>1.402866360489754e-05</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>***</t>
-        </is>
-      </c>
+        <v>-1.440190781179933</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.1501690903967529</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" t="b">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.002351445723019825</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.003769705794367909</v>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Rating per Item</t>
+          <t>Gini User</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.047388489638724</v>
+        <v>-0.01841455690641779</v>
       </c>
       <c r="C18" t="n">
-        <v>0.01520275080376517</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>*</t>
-        </is>
-      </c>
+        <v>-1.087839062825358</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.2769640088629442</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" t="b">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.001342959745836531</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.002152957682978653</v>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -731,52 +1027,178 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.06578658500369618</v>
+        <v>-0.01231460008971608</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0004021499541929435</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>***</t>
-        </is>
-      </c>
+        <v>-0.625045256172349</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.5321033930762189</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" t="b">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.0004437593223565823</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.0007114100369895212</v>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Mean Rating</t>
+          <t>Skewness of Long Tail Items</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.1431430193225595</v>
+        <v>0.005697126672619022</v>
       </c>
       <c r="C20" t="n">
-        <v>0.01923769355072301</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>*</t>
-        </is>
-      </c>
+        <v>0.4952573229829983</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.6205421313343513</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" t="b">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.0002786493964722722</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.0004467150715814287</v>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gini Item</t>
+          <t>Number of Items</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.1521256500697991</v>
+        <v>-0.007983051816839854</v>
       </c>
       <c r="C21" t="n">
-        <v>6.437913051178076e-10</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>***</t>
-        </is>
-      </c>
+        <v>-0.4714444997511217</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.6374402011624976</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" t="b">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.0002525043122253105</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.0004048007400639507</v>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Skewness of Popularity Bias</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0.003749251610095429</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.3173781059166024</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.7510320042011684</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="b">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.000114451515391247</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.0001834822452080619</v>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Standart Deviation of Rating</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>0.007523902613199159</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.2185253552546569</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.8270704719711039</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="b">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>5.426220419111645e-05</v>
+      </c>
+      <c r="H23" t="n">
+        <v>8.699011997254667e-05</v>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Shape</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>0.003187503775549111</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.1682545089331532</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.8664217215976106</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" t="b">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>3.216894214443476e-05</v>
+      </c>
+      <c r="H24" t="n">
+        <v>5.157144237410891e-05</v>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
